--- a/exports/trend_1d/HDFCAMC_full_report.xlsx
+++ b/exports/trend_1d/HDFCAMC_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q61"/>
+  <dimension ref="A1:U61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,25 +557,25 @@
         <v>8.43</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>43343</v>
+        <v>43346</v>
       </c>
       <c r="H2" t="n">
-        <v>871.4</v>
+        <v>836.7</v>
       </c>
       <c r="I2" t="n">
         <v>846.8163559999999</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K2" t="n">
-        <v>2.88</v>
+        <v>-1.22</v>
       </c>
       <c r="L2" t="n">
-        <v>0.93</v>
+        <v>1.45</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0.22</v>
       </c>
       <c r="N2" t="n">
         <v>3.99</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>12.07</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>43426</v>
+        <v>43430</v>
       </c>
       <c r="H3" t="n">
-        <v>683.1</v>
+        <v>707.5</v>
       </c>
       <c r="I3" t="n">
         <v>695.0696035385513</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="K3" t="n">
-        <v>18.36</v>
+        <v>15.44</v>
       </c>
       <c r="L3" t="n">
         <v>3.92</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>7.28</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>43458</v>
+        <v>43460</v>
       </c>
       <c r="H4" t="n">
-        <v>717.3</v>
+        <v>703.6</v>
       </c>
       <c r="I4" t="n">
         <v>704.1928434048134</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K4" t="n">
-        <v>1.39</v>
+        <v>-0.55</v>
       </c>
       <c r="L4" t="n">
         <v>3.18</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>9.43</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>43524</v>
+        <v>43525</v>
       </c>
       <c r="H5" t="n">
-        <v>658.1</v>
+        <v>677.7</v>
       </c>
       <c r="I5" t="n">
         <v>666.1284613844946</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K5" t="n">
-        <v>6.47</v>
+        <v>3.68</v>
       </c>
       <c r="L5" t="n">
         <v>4.8</v>
@@ -726,7 +785,7 @@
         <v>1.32</v>
       </c>
       <c r="N5" t="n">
-        <v>2.26</v>
+        <v>2.98</v>
       </c>
       <c r="O5" t="n">
         <v>-1.91</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>7.11</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>43634</v>
+        <v>43635</v>
       </c>
       <c r="H6" t="n">
-        <v>869</v>
+        <v>866.1</v>
       </c>
       <c r="I6" t="n">
         <v>868.0097545777319</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K6" t="n">
-        <v>28.23</v>
+        <v>27.8</v>
       </c>
       <c r="L6" t="n">
         <v>2.89</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>8.75</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>43641</v>
+        <v>43642</v>
       </c>
       <c r="H7" t="n">
-        <v>938</v>
+        <v>950.7</v>
       </c>
       <c r="I7" t="n">
         <v>941.9185987920373</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K7" t="n">
-        <v>-8.300000000000001</v>
+        <v>-9.77</v>
       </c>
       <c r="L7" t="n">
-        <v>9.380000000000001</v>
+        <v>10.06</v>
       </c>
       <c r="M7" t="n">
         <v>0.68</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>43643</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -876,25 +971,25 @@
         <v>8.68</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>43651</v>
+        <v>43654</v>
       </c>
       <c r="H8" t="n">
-        <v>948.3</v>
+        <v>914.5</v>
       </c>
       <c r="I8" t="n">
         <v>926.8877392393823</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.25</v>
+        <v>-3.81</v>
       </c>
       <c r="L8" t="n">
-        <v>1.69</v>
+        <v>4.73</v>
       </c>
       <c r="M8" t="n">
-        <v>0.35</v>
+        <v>0.73</v>
       </c>
       <c r="N8" t="n">
         <v>3.86</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>43643</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,28 +1040,28 @@
         <v>10.65</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>43663</v>
+        <v>43664</v>
       </c>
       <c r="H9" t="n">
-        <v>996.7</v>
+        <v>1042.2</v>
       </c>
       <c r="I9" t="n">
         <v>1011.921883856537</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K9" t="n">
-        <v>-8.99</v>
+        <v>-13.96</v>
       </c>
       <c r="L9" t="n">
-        <v>11.72</v>
+        <v>15.14</v>
       </c>
       <c r="M9" t="n">
         <v>2.35</v>
       </c>
       <c r="N9" t="n">
-        <v>4.25</v>
+        <v>4.57</v>
       </c>
       <c r="O9" t="n">
         <v>-3.56</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,25 +1109,25 @@
         <v>12.14</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>43803</v>
+        <v>43804</v>
       </c>
       <c r="H10" t="n">
-        <v>1604.9</v>
+        <v>1537.4</v>
       </c>
       <c r="I10" t="n">
         <v>1602.943323375558</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K10" t="n">
-        <v>53.99</v>
+        <v>47.51</v>
       </c>
       <c r="L10" t="n">
         <v>5.73</v>
       </c>
       <c r="M10" t="n">
-        <v>2.72</v>
+        <v>5</v>
       </c>
       <c r="N10" t="n">
         <v>4.92</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>92</v>
+        <v>93</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>6</v>
+      </c>
+      <c r="U10" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>14.2</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>43866</v>
+        <v>43867</v>
       </c>
       <c r="H11" t="n">
-        <v>1532</v>
+        <v>1593.6</v>
       </c>
       <c r="I11" t="n">
         <v>1570.03429338919</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K11" t="n">
-        <v>0.35</v>
+        <v>-3.66</v>
       </c>
       <c r="L11" t="n">
-        <v>2.61</v>
+        <v>4.2</v>
       </c>
       <c r="M11" t="n">
         <v>1.88</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>43825</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>10</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>43889</v>
+        <v>43892</v>
       </c>
       <c r="H12" t="n">
-        <v>1509</v>
+        <v>1465.4</v>
       </c>
       <c r="I12" t="n">
         <v>1500.087921059113</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K12" t="n">
-        <v>-5.31</v>
+        <v>-8.039999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>6.57</v>
+        <v>9.02</v>
       </c>
       <c r="M12" t="n">
         <v>2.98</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>12.94</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>43938</v>
+        <v>43941</v>
       </c>
       <c r="H13" t="n">
-        <v>1285.9</v>
+        <v>1341.2</v>
       </c>
       <c r="I13" t="n">
         <v>1290.184809617711</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K13" t="n">
-        <v>12.25</v>
+        <v>8.48</v>
       </c>
       <c r="L13" t="n">
         <v>5.55</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>19.19</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>43998</v>
+        <v>43999</v>
       </c>
       <c r="H14" t="n">
-        <v>1219.8</v>
+        <v>1160.1</v>
       </c>
       <c r="I14" t="n">
         <v>1165.930747816203</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K14" t="n">
-        <v>-9.050000000000001</v>
+        <v>-13.5</v>
       </c>
       <c r="L14" t="n">
         <v>24.81</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>13.44</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44064</v>
+        <v>44067</v>
       </c>
       <c r="H15" t="n">
-        <v>1152.3</v>
+        <v>1189</v>
       </c>
       <c r="I15" t="n">
         <v>1182.95650423325</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="K15" t="n">
-        <v>0.67</v>
+        <v>-2.49</v>
       </c>
       <c r="L15" t="n">
         <v>8.98</v>
@@ -1296,7 +1475,7 @@
         <v>2.17</v>
       </c>
       <c r="N15" t="n">
-        <v>2.03</v>
+        <v>3.18</v>
       </c>
       <c r="O15" t="n">
         <v>-4.89</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>6.9</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44088</v>
+        <v>44089</v>
       </c>
       <c r="H16" t="n">
-        <v>1128.8</v>
+        <v>1108.3</v>
       </c>
       <c r="I16" t="n">
         <v>1128.168060270631</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K16" t="n">
-        <v>-5.06</v>
+        <v>-6.79</v>
       </c>
       <c r="L16" t="n">
-        <v>5.68</v>
+        <v>6.96</v>
       </c>
       <c r="M16" t="n">
         <v>2.64</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44070</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>8.119999999999999</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44105</v>
+        <v>44109</v>
       </c>
       <c r="H17" t="n">
-        <v>1092.6</v>
+        <v>1104.8</v>
       </c>
       <c r="I17" t="n">
         <v>1097.2775487098</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K17" t="n">
-        <v>1.42</v>
+        <v>0.32</v>
       </c>
       <c r="L17" t="n">
         <v>2.43</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>9.24</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44218</v>
+        <v>44221</v>
       </c>
       <c r="H18" t="n">
-        <v>1489.4</v>
+        <v>1418.5</v>
       </c>
       <c r="I18" t="n">
         <v>1457.446689622382</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="K18" t="n">
-        <v>34.81</v>
+        <v>28.39</v>
       </c>
       <c r="L18" t="n">
         <v>3.23</v>
@@ -1467,7 +1682,7 @@
         <v>1.38</v>
       </c>
       <c r="N18" t="n">
-        <v>3.43</v>
+        <v>4.76</v>
       </c>
       <c r="O18" t="n">
         <v>1.12</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>12.54</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44257</v>
+        <v>44258</v>
       </c>
       <c r="H19" t="n">
-        <v>1409.2</v>
+        <v>1531.5</v>
       </c>
       <c r="I19" t="n">
         <v>1505.54423560443</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K19" t="n">
-        <v>0.66</v>
+        <v>-7.97</v>
       </c>
       <c r="L19" t="n">
-        <v>5.62</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="M19" t="n">
         <v>1.45</v>
       </c>
       <c r="N19" t="n">
-        <v>4.06</v>
+        <v>8.68</v>
       </c>
       <c r="O19" t="n">
         <v>-4.76</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>12.33</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44271</v>
+        <v>44272</v>
       </c>
       <c r="H20" t="n">
-        <v>1428.8</v>
+        <v>1399.9</v>
       </c>
       <c r="I20" t="n">
         <v>1401.687480548341</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K20" t="n">
-        <v>-6.71</v>
+        <v>-8.59</v>
       </c>
       <c r="L20" t="n">
-        <v>7.99</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="M20" t="n">
         <v>1.85</v>
       </c>
       <c r="N20" t="n">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="O20" t="n">
         <v>8.68</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>10.7</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>44343</v>
+        <v>44344</v>
       </c>
       <c r="H21" t="n">
-        <v>1364.2</v>
+        <v>1426.3</v>
       </c>
       <c r="I21" t="n">
         <v>1404.621966925189</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K21" t="n">
-        <v>2.55</v>
+        <v>-1.89</v>
       </c>
       <c r="L21" t="n">
         <v>4.65</v>
@@ -1638,7 +1889,7 @@
         <v>1.71</v>
       </c>
       <c r="N21" t="n">
-        <v>3.66</v>
+        <v>4.55</v>
       </c>
       <c r="O21" t="n">
         <v>-2.02</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>4</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>7.53</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>44377</v>
+        <v>44378</v>
       </c>
       <c r="H22" t="n">
-        <v>1401.3</v>
+        <v>1390.1</v>
       </c>
       <c r="I22" t="n">
         <v>1393.031283589679</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.75</v>
+        <v>-2.54</v>
       </c>
       <c r="L22" t="n">
         <v>3.53</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>44371</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>6.72</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>44391</v>
+        <v>44392</v>
       </c>
       <c r="H23" t="n">
-        <v>1420.4</v>
+        <v>1482.1</v>
       </c>
       <c r="I23" t="n">
         <v>1468.304911156602</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.18</v>
+        <v>-6.62</v>
       </c>
       <c r="L23" t="n">
-        <v>2.57</v>
+        <v>7.01</v>
       </c>
       <c r="M23" t="n">
         <v>0.72</v>
       </c>
       <c r="N23" t="n">
-        <v>1.26</v>
+        <v>4.34</v>
       </c>
       <c r="O23" t="n">
         <v>-0.8</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>7.81</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>44396</v>
+        <v>44397</v>
       </c>
       <c r="H24" t="n">
-        <v>1437.1</v>
+        <v>1382.3</v>
       </c>
       <c r="I24" t="n">
         <v>1414.113057071458</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K24" t="n">
-        <v>-3.04</v>
+        <v>-6.73</v>
       </c>
       <c r="L24" t="n">
-        <v>4.32</v>
+        <v>7.17</v>
       </c>
       <c r="M24" t="n">
         <v>1.41</v>
       </c>
       <c r="N24" t="n">
-        <v>3.29</v>
+        <v>3.81</v>
       </c>
       <c r="O24" t="n">
         <v>4.34</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>10.52</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>44435</v>
+        <v>44438</v>
       </c>
       <c r="H25" t="n">
-        <v>1455.2</v>
+        <v>1470.8</v>
       </c>
       <c r="I25" t="n">
         <v>1460.443015859991</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K25" t="n">
-        <v>-5.27</v>
+        <v>-6.4</v>
       </c>
       <c r="L25" t="n">
-        <v>6.08</v>
+        <v>7.47</v>
       </c>
       <c r="M25" t="n">
         <v>1.25</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,28 +2213,28 @@
         <v>6.24</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>44467</v>
+        <v>44468</v>
       </c>
       <c r="H26" t="n">
-        <v>1476.7</v>
+        <v>1395.5</v>
       </c>
       <c r="I26" t="n">
         <v>1452.609933368315</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K26" t="n">
-        <v>0.4</v>
+        <v>-5.12</v>
       </c>
       <c r="L26" t="n">
-        <v>0.73</v>
+        <v>6.09</v>
       </c>
       <c r="M26" t="n">
-        <v>0.44</v>
+        <v>5.37</v>
       </c>
       <c r="N26" t="n">
-        <v>2.96</v>
+        <v>5.5</v>
       </c>
       <c r="O26" t="n">
         <v>1.07</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>10.78</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>44651</v>
+        <v>44652</v>
       </c>
       <c r="H27" t="n">
-        <v>1030.5</v>
+        <v>1093.6</v>
       </c>
       <c r="I27" t="n">
         <v>1077.167989484407</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K27" t="n">
-        <v>26.16</v>
+        <v>21.63</v>
       </c>
       <c r="L27" t="n">
         <v>2.52</v>
@@ -1980,7 +2303,7 @@
         <v>2.43</v>
       </c>
       <c r="N27" t="n">
-        <v>3.59</v>
+        <v>6.12</v>
       </c>
       <c r="O27" t="n">
         <v>-5.5</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>126</v>
+        <v>127</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>8</v>
+      </c>
+      <c r="U27" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>11.85</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>44669</v>
+        <v>44670</v>
       </c>
       <c r="H28" t="n">
-        <v>1049.1</v>
+        <v>1013.3</v>
       </c>
       <c r="I28" t="n">
         <v>1021.466379324797</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K28" t="n">
-        <v>-4.07</v>
+        <v>-7.34</v>
       </c>
       <c r="L28" t="n">
-        <v>5.46</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="M28" t="n">
         <v>2.08</v>
       </c>
       <c r="N28" t="n">
-        <v>1.62</v>
+        <v>3.41</v>
       </c>
       <c r="O28" t="n">
         <v>6.12</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>12.14</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>44711</v>
+        <v>44712</v>
       </c>
       <c r="H29" t="n">
-        <v>881.7</v>
+        <v>911.1</v>
       </c>
       <c r="I29" t="n">
         <v>906.1682339666462</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K29" t="n">
-        <v>12.99</v>
+        <v>10.09</v>
       </c>
       <c r="L29" t="n">
         <v>4.74</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>11.59</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>44819</v>
+        <v>44820</v>
       </c>
       <c r="H30" t="n">
-        <v>965.4</v>
+        <v>933.6</v>
       </c>
       <c r="I30" t="n">
         <v>945.3664178112539</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K30" t="n">
-        <v>5.96</v>
+        <v>2.47</v>
       </c>
       <c r="L30" t="n">
         <v>9.67</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>4</v>
+      </c>
+      <c r="U30" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>9.289999999999999</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>44853</v>
+        <v>44854</v>
       </c>
       <c r="H31" t="n">
-        <v>941.4</v>
+        <v>977.6</v>
       </c>
       <c r="I31" t="n">
         <v>951.7122609163782</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.84</v>
+        <v>-4.71</v>
       </c>
       <c r="L31" t="n">
-        <v>3.72</v>
+        <v>5.4</v>
       </c>
       <c r="M31" t="n">
         <v>1.44</v>
       </c>
       <c r="N31" t="n">
-        <v>2.99</v>
+        <v>3.85</v>
       </c>
       <c r="O31" t="n">
         <v>-3.29</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>10.26</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44917</v>
+        <v>44918</v>
       </c>
       <c r="H32" t="n">
-        <v>1048.6</v>
+        <v>997.2</v>
       </c>
       <c r="I32" t="n">
         <v>1026.802475822868</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K32" t="n">
-        <v>7.26</v>
+        <v>2</v>
       </c>
       <c r="L32" t="n">
         <v>5.85</v>
       </c>
       <c r="M32" t="n">
-        <v>0.83</v>
+        <v>1.26</v>
       </c>
       <c r="N32" t="n">
-        <v>2.05</v>
+        <v>4.9</v>
       </c>
       <c r="O32" t="n">
         <v>3.85</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>11.4</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45029</v>
+        <v>45033</v>
       </c>
       <c r="H33" t="n">
-        <v>860.7</v>
+        <v>868</v>
       </c>
       <c r="I33" t="n">
         <v>861.7661092892945</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="K33" t="n">
-        <v>13.69</v>
+        <v>12.96</v>
       </c>
       <c r="L33" t="n">
         <v>7.65</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>5</v>
+      </c>
+      <c r="U33" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>6.92</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45069</v>
+        <v>45070</v>
       </c>
       <c r="H34" t="n">
-        <v>848.4</v>
+        <v>836.7</v>
       </c>
       <c r="I34" t="n">
         <v>841.2944532192793</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K34" t="n">
-        <v>-2.26</v>
+        <v>-3.61</v>
       </c>
       <c r="L34" t="n">
         <v>4.4</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>6.63</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45072</v>
+        <v>45075</v>
       </c>
       <c r="H35" t="n">
-        <v>891.5</v>
+        <v>899.8</v>
       </c>
       <c r="I35" t="n">
         <v>892.202865536693</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K35" t="n">
-        <v>-6.55</v>
+        <v>-7.54</v>
       </c>
       <c r="L35" t="n">
-        <v>6.79</v>
+        <v>8.59</v>
       </c>
       <c r="M35" t="n">
         <v>0.17</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>6.67</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45370</v>
+        <v>45371</v>
       </c>
       <c r="H36" t="n">
-        <v>1761</v>
+        <v>1734.6</v>
       </c>
       <c r="I36" t="n">
         <v>1736.960786359545</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="K36" t="n">
-        <v>95.70999999999999</v>
+        <v>92.78</v>
       </c>
       <c r="L36" t="n">
         <v>1.24</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>204</v>
+        <v>205</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>10</v>
+      </c>
+      <c r="U36" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>10.54</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45412</v>
+        <v>45414</v>
       </c>
       <c r="H37" t="n">
-        <v>1870.6</v>
+        <v>1891.6</v>
       </c>
       <c r="I37" t="n">
         <v>1877.333718183369</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K37" t="n">
-        <v>-7.84</v>
+        <v>-9.050000000000001</v>
       </c>
       <c r="L37" t="n">
-        <v>9.199999999999999</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="M37" t="n">
         <v>1.19</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>7.57</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45420</v>
+        <v>45421</v>
       </c>
       <c r="H38" t="n">
-        <v>1784.5</v>
+        <v>1737</v>
       </c>
       <c r="I38" t="n">
         <v>1758.098297974912</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K38" t="n">
-        <v>-5.66</v>
+        <v>-8.17</v>
       </c>
       <c r="L38" t="n">
-        <v>5.87</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="M38" t="n">
         <v>-0</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>9.949999999999999</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45439</v>
+        <v>45440</v>
       </c>
       <c r="H39" t="n">
-        <v>1882.8</v>
+        <v>1926.9</v>
       </c>
       <c r="I39" t="n">
         <v>1887.584121975915</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K39" t="n">
-        <v>-8.390000000000001</v>
+        <v>-10.93</v>
       </c>
       <c r="L39" t="n">
-        <v>11.16</v>
+        <v>11.74</v>
       </c>
       <c r="M39" t="n">
         <v>0.57</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>8.359999999999999</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="H40" t="n">
-        <v>1964.5</v>
+        <v>1660.7</v>
       </c>
       <c r="I40" t="n">
         <v>1774.179686882038</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K40" t="n">
-        <v>1.95</v>
+        <v>-13.81</v>
       </c>
       <c r="L40" t="n">
-        <v>7.14</v>
+        <v>14.86</v>
       </c>
       <c r="M40" t="n">
         <v>0.79</v>
       </c>
       <c r="N40" t="n">
-        <v>3.72</v>
+        <v>15.46</v>
       </c>
       <c r="O40" t="n">
         <v>2.34</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>24.61</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45476</v>
+        <v>45477</v>
       </c>
       <c r="H41" t="n">
-        <v>1981.7</v>
+        <v>2027.2</v>
       </c>
       <c r="I41" t="n">
         <v>2010.747453625549</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K41" t="n">
-        <v>-19.33</v>
+        <v>-22.07</v>
       </c>
       <c r="L41" t="n">
-        <v>21.36</v>
+        <v>22.86</v>
       </c>
       <c r="M41" t="n">
         <v>1.45</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>10.1</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45566</v>
+        <v>45568</v>
       </c>
       <c r="H42" t="n">
-        <v>2096.6</v>
+        <v>2029.6</v>
       </c>
       <c r="I42" t="n">
         <v>2038.289244453529</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K42" t="n">
-        <v>3.42</v>
+        <v>0.12</v>
       </c>
       <c r="L42" t="n">
         <v>12.26</v>
@@ -2835,7 +3338,7 @@
         <v>1.8</v>
       </c>
       <c r="N42" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="O42" t="n">
         <v>2.3</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>4</v>
+      </c>
+      <c r="U42" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>8.93</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45579</v>
+        <v>45580</v>
       </c>
       <c r="H43" t="n">
-        <v>2152.9</v>
+        <v>2187.7</v>
       </c>
       <c r="I43" t="n">
         <v>2152.94581792044</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K43" t="n">
-        <v>-6.08</v>
+        <v>-7.79</v>
       </c>
       <c r="L43" t="n">
-        <v>6.53</v>
+        <v>8.94</v>
       </c>
       <c r="M43" t="n">
         <v>1.46</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>8.07</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45589</v>
+        <v>45590</v>
       </c>
       <c r="H44" t="n">
-        <v>2129.9</v>
+        <v>2085.4</v>
       </c>
       <c r="I44" t="n">
         <v>2089.871884535689</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K44" t="n">
-        <v>-2.64</v>
+        <v>-4.68</v>
       </c>
       <c r="L44" t="n">
-        <v>4.25</v>
+        <v>5.48</v>
       </c>
       <c r="M44" t="n">
         <v>0.65</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>12.17</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45636</v>
+        <v>45637</v>
       </c>
       <c r="H45" t="n">
-        <v>2140.2</v>
+        <v>2182.3</v>
       </c>
       <c r="I45" t="n">
         <v>2179.127003935484</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K45" t="n">
-        <v>-2.63</v>
+        <v>-4.65</v>
       </c>
       <c r="L45" t="n">
         <v>4.86</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,22 +3593,22 @@
         <v>7.7</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45649</v>
+        <v>45650</v>
       </c>
       <c r="H46" t="n">
-        <v>2040.9</v>
+        <v>2025.2</v>
       </c>
       <c r="I46" t="n">
         <v>2036.41941956181</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K46" t="n">
-        <v>-6.48</v>
+        <v>-7.2</v>
       </c>
       <c r="L46" t="n">
-        <v>7.24</v>
+        <v>7.33</v>
       </c>
       <c r="M46" t="n">
         <v>1.31</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>8.390000000000001</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45737</v>
+        <v>45740</v>
       </c>
       <c r="H47" t="n">
-        <v>1918.5</v>
+        <v>1969.4</v>
       </c>
       <c r="I47" t="n">
         <v>1924.663202186224</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="K47" t="n">
-        <v>5.27</v>
+        <v>2.76</v>
       </c>
       <c r="L47" t="n">
         <v>2.56</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>4</v>
+      </c>
+      <c r="U47" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>9.949999999999999</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45751</v>
+        <v>45754</v>
       </c>
       <c r="H48" t="n">
-        <v>1876</v>
+        <v>1792.3</v>
       </c>
       <c r="I48" t="n">
         <v>1807.35529018199</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K48" t="n">
-        <v>-4.74</v>
+        <v>-8.99</v>
       </c>
       <c r="L48" t="n">
-        <v>5.39</v>
+        <v>13.02</v>
       </c>
       <c r="M48" t="n">
-        <v>0.95</v>
+        <v>6.55</v>
       </c>
       <c r="N48" t="n">
-        <v>3.4</v>
+        <v>4.46</v>
       </c>
       <c r="O48" t="n">
         <v>2.65</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>9.98</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45758</v>
+        <v>45762</v>
       </c>
       <c r="H49" t="n">
-        <v>1915.1</v>
+        <v>1985.1</v>
       </c>
       <c r="I49" t="n">
         <v>1971.155639967354</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K49" t="n">
-        <v>-6.85</v>
+        <v>-10.76</v>
       </c>
       <c r="L49" t="n">
-        <v>8.029999999999999</v>
+        <v>10.97</v>
       </c>
       <c r="M49" t="n">
         <v>1.28</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>12.38</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45897</v>
+        <v>45898</v>
       </c>
       <c r="H50" t="n">
-        <v>2731.3</v>
+        <v>2673</v>
       </c>
       <c r="I50" t="n">
         <v>2708.814217063594</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="K50" t="n">
-        <v>37.59</v>
+        <v>34.65</v>
       </c>
       <c r="L50" t="n">
         <v>3.08</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>94</v>
+        <v>95</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>6</v>
+      </c>
+      <c r="U50" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>8.550000000000001</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="H51" t="n">
-        <v>2486.8</v>
+        <v>2664.6</v>
       </c>
       <c r="I51" t="n">
         <v>2624.608734783672</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K51" t="n">
-        <v>6.97</v>
+        <v>0.31</v>
       </c>
       <c r="L51" t="n">
         <v>8.619999999999999</v>
       </c>
       <c r="M51" t="n">
-        <v>0.99</v>
+        <v>2.43</v>
       </c>
       <c r="N51" t="n">
-        <v>3.04</v>
+        <v>7.15</v>
       </c>
       <c r="O51" t="n">
         <v>-2.13</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>4</v>
+      </c>
+      <c r="U51" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>9.43</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="H52" t="n">
-        <v>2469.4</v>
+        <v>2434.3</v>
       </c>
       <c r="I52" t="n">
         <v>2447.404922918652</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K52" t="n">
-        <v>-7.33</v>
+        <v>-8.640000000000001</v>
       </c>
       <c r="L52" t="n">
-        <v>7.52</v>
+        <v>9.49</v>
       </c>
       <c r="M52" t="n">
         <v>0.42</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,25 +4076,25 @@
         <v>7.29</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="H53" t="n">
-        <v>2515.3</v>
+        <v>2614.1</v>
       </c>
       <c r="I53" t="n">
         <v>2574.350527188063</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K53" t="n">
-        <v>-3.33</v>
+        <v>-7.39</v>
       </c>
       <c r="L53" t="n">
-        <v>8.380000000000001</v>
+        <v>11.35</v>
       </c>
       <c r="M53" t="n">
-        <v>1.33</v>
+        <v>6.99</v>
       </c>
       <c r="N53" t="n">
         <v>4.46</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,25 +4145,25 @@
         <v>8.66</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="H54" t="n">
-        <v>2640.8</v>
+        <v>2593.1</v>
       </c>
       <c r="I54" t="n">
         <v>2596.459694892522</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K54" t="n">
-        <v>1.02</v>
+        <v>-0.8</v>
       </c>
       <c r="L54" t="n">
-        <v>0.47</v>
+        <v>2.62</v>
       </c>
       <c r="M54" t="n">
-        <v>1.28</v>
+        <v>2.73</v>
       </c>
       <c r="N54" t="n">
         <v>2.86</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>7.59</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="H55" t="n">
-        <v>2295</v>
+        <v>2485</v>
       </c>
       <c r="I55" t="n">
         <v>2470.413537778564</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K55" t="n">
-        <v>11.5</v>
+        <v>4.17</v>
       </c>
       <c r="L55" t="n">
         <v>1.52</v>
       </c>
       <c r="M55" t="n">
-        <v>3.09</v>
+        <v>6.17</v>
       </c>
       <c r="N55" t="n">
-        <v>5.6</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="O55" t="n">
         <v>-1.81</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>14.01</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="H56" t="n">
-        <v>2617.1</v>
+        <v>2548.9</v>
       </c>
       <c r="I56" t="n">
         <v>2554.359167564804</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K56" t="n">
-        <v>5.32</v>
+        <v>2.57</v>
       </c>
       <c r="L56" t="n">
         <v>4.25</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>3</v>
+      </c>
+      <c r="U56" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>11.27</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="H57" t="n">
-        <v>2622.9</v>
+        <v>2658.6</v>
       </c>
       <c r="I57" t="n">
         <v>2634.635675146796</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K57" t="n">
-        <v>-2.9</v>
+        <v>-4.3</v>
       </c>
       <c r="L57" t="n">
-        <v>4.14</v>
+        <v>4.71</v>
       </c>
       <c r="M57" t="n">
         <v>1.8</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,22 +4421,22 @@
         <v>9.56</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="H58" t="n">
-        <v>2644.9</v>
+        <v>2581.1</v>
       </c>
       <c r="I58" t="n">
         <v>2594.742760968944</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K58" t="n">
-        <v>-0.52</v>
+        <v>-2.92</v>
       </c>
       <c r="L58" t="n">
-        <v>2.67</v>
+        <v>3.02</v>
       </c>
       <c r="M58" t="n">
         <v>1.04</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>12.22</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="H59" t="n">
-        <v>2618</v>
+        <v>2698</v>
       </c>
       <c r="I59" t="n">
         <v>2642.171855475293</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K59" t="n">
-        <v>-1.43</v>
+        <v>-4.53</v>
       </c>
       <c r="L59" t="n">
-        <v>4.41</v>
+        <v>4.53</v>
       </c>
       <c r="M59" t="n">
         <v>0.93</v>
       </c>
       <c r="N59" t="n">
-        <v>2.83</v>
+        <v>3.06</v>
       </c>
       <c r="O59" t="n">
         <v>-2.41</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>7.57</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="H60" t="n">
-        <v>2525.7</v>
+        <v>2510.8</v>
       </c>
       <c r="I60" t="n">
         <v>2517.518139092027</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K60" t="n">
-        <v>-6.39</v>
+        <v>-6.94</v>
       </c>
       <c r="L60" t="n">
         <v>8.19</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3921,6 +4652,14 @@
       <c r="Q61" t="n">
         <v>37</v>
       </c>
+      <c r="R61" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7417,7 +8156,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>48.1</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="6">
@@ -7427,7 +8166,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7">
@@ -7437,7 +8176,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="8">
@@ -7447,7 +8186,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -7457,7 +8196,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>63.5</v>
+        <v>64.5</v>
       </c>
     </row>
     <row r="10">
@@ -7467,7 +8206,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>109.2</v>
+        <v>111.2</v>
       </c>
     </row>
     <row r="11">
@@ -7507,7 +8246,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.02</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="15">
@@ -7517,7 +8256,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6.96</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="16">
@@ -7527,7 +8266,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.98</v>
+        <v>-2.3</v>
       </c>
     </row>
     <row r="17">
@@ -7537,7 +8276,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>95.70999999999999</v>
+        <v>92.78</v>
       </c>
     </row>
     <row r="18">
@@ -7547,7 +8286,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>47.5</v>
+        <v>32.2</v>
       </c>
     </row>
     <row r="19">
@@ -7557,7 +8296,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.94</v>
+        <v>7.19</v>
       </c>
     </row>
     <row r="20">
@@ -7567,7 +8306,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.39</v>
+        <v>6.09</v>
       </c>
     </row>
     <row r="21">
@@ -7587,7 +8326,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23">
@@ -7597,7 +8336,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24">
@@ -7607,7 +8346,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="25">
@@ -7617,7 +8356,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5.41</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="26">
@@ -7627,7 +8366,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.79</v>
+        <v>4.53</v>
       </c>
     </row>
     <row r="27">
@@ -7637,7 +8376,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>8.220000000000001</v>
+        <v>15.46</v>
       </c>
     </row>
     <row r="28">
@@ -7647,7 +8386,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29">
